--- a/data/wind tunnel/CURRENT WIND TUNNEL GENERATION MEANS.xlsx
+++ b/data/wind tunnel/CURRENT WIND TUNNEL GENERATION MEANS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10909"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10927"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/wind-tunnel-flies/data/wind tunnel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B3219EC-95D6-204C-9CB0-FEBB1886A020}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED4BB4B5-20B6-9C48-BB2A-A5EA61441344}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="25920" windowHeight="13440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5345,7 +5345,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:L443"/>
+  <dimension ref="A1:L505"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="6.33203125" style="2" customWidth="1"/>
@@ -5919,7 +5919,9 @@
         <v>193.77</v>
       </c>
       <c r="G25" s="4"/>
-      <c r="H25" s="5"/>
+      <c r="H25" s="5">
+        <v>34651</v>
+      </c>
       <c r="I25" s="5"/>
     </row>
     <row r="26" spans="1:9" s="1" customFormat="1" ht="19">
@@ -6383,7 +6385,9 @@
       <c r="G45" s="4">
         <v>176.67</v>
       </c>
-      <c r="H45" s="5"/>
+      <c r="H45" s="5">
+        <v>34973</v>
+      </c>
       <c r="I45" s="5"/>
     </row>
     <row r="46" spans="1:9" s="1" customFormat="1" ht="19">
@@ -17097,7 +17101,7 @@
         <v>236.33500000000001</v>
       </c>
     </row>
-    <row r="434" spans="1:7">
+    <row r="434" spans="1:9">
       <c r="A434" s="2">
         <v>709</v>
       </c>
@@ -17112,7 +17116,7 @@
         <v>226.01</v>
       </c>
     </row>
-    <row r="435" spans="1:7">
+    <row r="435" spans="1:9">
       <c r="A435" s="2">
         <v>710</v>
       </c>
@@ -17127,7 +17131,7 @@
         <v>200.04499999999999</v>
       </c>
     </row>
-    <row r="436" spans="1:7">
+    <row r="436" spans="1:9">
       <c r="A436" s="2">
         <v>711</v>
       </c>
@@ -17142,7 +17146,7 @@
         <v>227.47499999999999</v>
       </c>
     </row>
-    <row r="437" spans="1:7">
+    <row r="437" spans="1:9">
       <c r="A437" s="2">
         <v>712</v>
       </c>
@@ -17157,7 +17161,7 @@
         <v>272.76499999999999</v>
       </c>
     </row>
-    <row r="438" spans="1:7">
+    <row r="438" spans="1:9">
       <c r="A438" s="2">
         <v>713</v>
       </c>
@@ -17182,7 +17186,7 @@
         <v>268.96000000000004</v>
       </c>
     </row>
-    <row r="439" spans="1:7">
+    <row r="439" spans="1:9">
       <c r="A439" s="2">
         <v>714</v>
       </c>
@@ -17197,7 +17201,7 @@
         <v>265.17999999999995</v>
       </c>
     </row>
-    <row r="441" spans="1:7">
+    <row r="441" spans="1:9">
       <c r="A441" s="2">
         <v>716</v>
       </c>
@@ -17212,7 +17216,7 @@
         <v>299.07000000000005</v>
       </c>
     </row>
-    <row r="442" spans="1:7">
+    <row r="442" spans="1:9">
       <c r="A442" s="2">
         <v>717</v>
       </c>
@@ -17227,7 +17231,7 @@
         <v>287.57499999999999</v>
       </c>
     </row>
-    <row r="443" spans="1:7">
+    <row r="443" spans="1:9">
       <c r="A443" s="2">
         <v>718</v>
       </c>
@@ -17250,6 +17254,561 @@
       <c r="G443" s="4">
         <f>AVERAGE(D443:E443)</f>
         <v>296.77499999999998</v>
+      </c>
+      <c r="I443" s="5">
+        <v>42925</v>
+      </c>
+    </row>
+    <row r="444" spans="1:9">
+      <c r="A444" s="2">
+        <f>A443+1</f>
+        <v>719</v>
+      </c>
+    </row>
+    <row r="445" spans="1:9">
+      <c r="A445" s="2">
+        <f t="shared" ref="A445:A508" si="237">A444+1</f>
+        <v>720</v>
+      </c>
+    </row>
+    <row r="446" spans="1:9">
+      <c r="A446" s="2">
+        <f t="shared" si="237"/>
+        <v>721</v>
+      </c>
+    </row>
+    <row r="447" spans="1:9">
+      <c r="A447" s="2">
+        <f t="shared" si="237"/>
+        <v>722</v>
+      </c>
+    </row>
+    <row r="448" spans="1:9">
+      <c r="A448" s="2">
+        <f t="shared" si="237"/>
+        <v>723</v>
+      </c>
+    </row>
+    <row r="449" spans="1:1">
+      <c r="A449" s="2">
+        <f t="shared" si="237"/>
+        <v>724</v>
+      </c>
+    </row>
+    <row r="450" spans="1:1">
+      <c r="A450" s="2">
+        <f t="shared" si="237"/>
+        <v>725</v>
+      </c>
+    </row>
+    <row r="451" spans="1:1">
+      <c r="A451" s="2">
+        <f t="shared" si="237"/>
+        <v>726</v>
+      </c>
+    </row>
+    <row r="452" spans="1:1">
+      <c r="A452" s="2">
+        <f t="shared" si="237"/>
+        <v>727</v>
+      </c>
+    </row>
+    <row r="453" spans="1:1">
+      <c r="A453" s="2">
+        <f t="shared" si="237"/>
+        <v>728</v>
+      </c>
+    </row>
+    <row r="454" spans="1:1">
+      <c r="A454" s="2">
+        <f t="shared" si="237"/>
+        <v>729</v>
+      </c>
+    </row>
+    <row r="455" spans="1:1">
+      <c r="A455" s="2">
+        <f t="shared" si="237"/>
+        <v>730</v>
+      </c>
+    </row>
+    <row r="456" spans="1:1">
+      <c r="A456" s="2">
+        <f t="shared" si="237"/>
+        <v>731</v>
+      </c>
+    </row>
+    <row r="457" spans="1:1">
+      <c r="A457" s="2">
+        <f t="shared" si="237"/>
+        <v>732</v>
+      </c>
+    </row>
+    <row r="458" spans="1:1">
+      <c r="A458" s="2">
+        <f t="shared" si="237"/>
+        <v>733</v>
+      </c>
+    </row>
+    <row r="459" spans="1:1">
+      <c r="A459" s="2">
+        <f t="shared" si="237"/>
+        <v>734</v>
+      </c>
+    </row>
+    <row r="460" spans="1:1">
+      <c r="A460" s="2">
+        <f t="shared" si="237"/>
+        <v>735</v>
+      </c>
+    </row>
+    <row r="461" spans="1:1">
+      <c r="A461" s="2">
+        <f t="shared" si="237"/>
+        <v>736</v>
+      </c>
+    </row>
+    <row r="462" spans="1:1">
+      <c r="A462" s="2">
+        <f t="shared" si="237"/>
+        <v>737</v>
+      </c>
+    </row>
+    <row r="463" spans="1:1">
+      <c r="A463" s="2">
+        <f t="shared" si="237"/>
+        <v>738</v>
+      </c>
+    </row>
+    <row r="464" spans="1:1">
+      <c r="A464" s="2">
+        <f t="shared" si="237"/>
+        <v>739</v>
+      </c>
+    </row>
+    <row r="465" spans="1:1">
+      <c r="A465" s="2">
+        <f t="shared" si="237"/>
+        <v>740</v>
+      </c>
+    </row>
+    <row r="466" spans="1:1">
+      <c r="A466" s="2">
+        <f t="shared" si="237"/>
+        <v>741</v>
+      </c>
+    </row>
+    <row r="467" spans="1:1">
+      <c r="A467" s="2">
+        <f t="shared" si="237"/>
+        <v>742</v>
+      </c>
+    </row>
+    <row r="468" spans="1:1">
+      <c r="A468" s="2">
+        <f t="shared" si="237"/>
+        <v>743</v>
+      </c>
+    </row>
+    <row r="469" spans="1:1">
+      <c r="A469" s="2">
+        <f t="shared" si="237"/>
+        <v>744</v>
+      </c>
+    </row>
+    <row r="470" spans="1:1">
+      <c r="A470" s="2">
+        <f t="shared" si="237"/>
+        <v>745</v>
+      </c>
+    </row>
+    <row r="471" spans="1:1">
+      <c r="A471" s="2">
+        <f t="shared" si="237"/>
+        <v>746</v>
+      </c>
+    </row>
+    <row r="472" spans="1:1">
+      <c r="A472" s="2">
+        <f t="shared" si="237"/>
+        <v>747</v>
+      </c>
+    </row>
+    <row r="473" spans="1:1">
+      <c r="A473" s="2">
+        <f t="shared" si="237"/>
+        <v>748</v>
+      </c>
+    </row>
+    <row r="474" spans="1:1">
+      <c r="A474" s="2">
+        <f t="shared" si="237"/>
+        <v>749</v>
+      </c>
+    </row>
+    <row r="475" spans="1:1">
+      <c r="A475" s="2">
+        <f t="shared" si="237"/>
+        <v>750</v>
+      </c>
+    </row>
+    <row r="476" spans="1:1">
+      <c r="A476" s="2">
+        <f t="shared" si="237"/>
+        <v>751</v>
+      </c>
+    </row>
+    <row r="477" spans="1:1">
+      <c r="A477" s="2">
+        <f t="shared" si="237"/>
+        <v>752</v>
+      </c>
+    </row>
+    <row r="478" spans="1:1">
+      <c r="A478" s="2">
+        <f t="shared" si="237"/>
+        <v>753</v>
+      </c>
+    </row>
+    <row r="479" spans="1:1">
+      <c r="A479" s="2">
+        <f t="shared" si="237"/>
+        <v>754</v>
+      </c>
+    </row>
+    <row r="480" spans="1:1">
+      <c r="A480" s="2">
+        <f t="shared" si="237"/>
+        <v>755</v>
+      </c>
+    </row>
+    <row r="481" spans="1:9">
+      <c r="A481" s="2">
+        <f t="shared" si="237"/>
+        <v>756</v>
+      </c>
+    </row>
+    <row r="482" spans="1:9">
+      <c r="A482" s="2">
+        <f t="shared" si="237"/>
+        <v>757</v>
+      </c>
+    </row>
+    <row r="483" spans="1:9">
+      <c r="A483" s="2">
+        <f t="shared" si="237"/>
+        <v>758</v>
+      </c>
+    </row>
+    <row r="484" spans="1:9">
+      <c r="A484" s="2">
+        <f t="shared" si="237"/>
+        <v>759</v>
+      </c>
+      <c r="D484" s="3">
+        <v>228.67</v>
+      </c>
+      <c r="E484" s="3">
+        <v>241.43</v>
+      </c>
+      <c r="I484" s="5">
+        <v>43499</v>
+      </c>
+    </row>
+    <row r="485" spans="1:9">
+      <c r="A485" s="2">
+        <f t="shared" si="237"/>
+        <v>760</v>
+      </c>
+    </row>
+    <row r="486" spans="1:9">
+      <c r="A486" s="2">
+        <f t="shared" si="237"/>
+        <v>761</v>
+      </c>
+      <c r="D486" s="3">
+        <v>321.81</v>
+      </c>
+      <c r="E486" s="3">
+        <v>251.45</v>
+      </c>
+      <c r="I486" s="5">
+        <v>43527</v>
+      </c>
+    </row>
+    <row r="487" spans="1:9">
+      <c r="A487" s="2">
+        <f t="shared" si="237"/>
+        <v>762</v>
+      </c>
+    </row>
+    <row r="488" spans="1:9">
+      <c r="A488" s="2">
+        <f t="shared" si="237"/>
+        <v>763</v>
+      </c>
+      <c r="D488" s="3">
+        <v>264.47000000000003</v>
+      </c>
+      <c r="E488" s="3">
+        <v>272.87</v>
+      </c>
+      <c r="I488" s="5">
+        <v>43554</v>
+      </c>
+    </row>
+    <row r="489" spans="1:9">
+      <c r="A489" s="2">
+        <f t="shared" si="237"/>
+        <v>764</v>
+      </c>
+    </row>
+    <row r="490" spans="1:9">
+      <c r="A490" s="2">
+        <f t="shared" si="237"/>
+        <v>765</v>
+      </c>
+      <c r="D490" s="3">
+        <v>252.14</v>
+      </c>
+      <c r="E490" s="3">
+        <v>256.13</v>
+      </c>
+      <c r="I490" s="5">
+        <v>43583</v>
+      </c>
+    </row>
+    <row r="491" spans="1:9">
+      <c r="A491" s="2">
+        <f t="shared" si="237"/>
+        <v>766</v>
+      </c>
+    </row>
+    <row r="492" spans="1:9">
+      <c r="A492" s="2">
+        <f t="shared" si="237"/>
+        <v>767</v>
+      </c>
+    </row>
+    <row r="493" spans="1:9">
+      <c r="A493" s="2">
+        <f t="shared" si="237"/>
+        <v>768</v>
+      </c>
+      <c r="D493" s="3">
+        <v>229.33</v>
+      </c>
+      <c r="E493" s="3">
+        <v>215.19</v>
+      </c>
+      <c r="I493" s="5">
+        <v>43625</v>
+      </c>
+    </row>
+    <row r="494" spans="1:9">
+      <c r="A494" s="2">
+        <f t="shared" si="237"/>
+        <v>769</v>
+      </c>
+      <c r="B494" s="3">
+        <v>282.66000000000003</v>
+      </c>
+      <c r="C494" s="3">
+        <v>281.45999999999998</v>
+      </c>
+      <c r="D494" s="3">
+        <v>286.17</v>
+      </c>
+      <c r="E494" s="3">
+        <v>273.41000000000003</v>
+      </c>
+      <c r="H494" s="5">
+        <v>43632</v>
+      </c>
+      <c r="I494" s="5">
+        <v>43639</v>
+      </c>
+    </row>
+    <row r="495" spans="1:9">
+      <c r="A495" s="2">
+        <f t="shared" si="237"/>
+        <v>770</v>
+      </c>
+      <c r="B495" s="3">
+        <v>291.38</v>
+      </c>
+      <c r="C495" s="3">
+        <v>281.7</v>
+      </c>
+      <c r="H495" s="5">
+        <v>43646</v>
+      </c>
+    </row>
+    <row r="496" spans="1:9">
+      <c r="A496" s="2">
+        <f t="shared" si="237"/>
+        <v>771</v>
+      </c>
+      <c r="B496" s="3">
+        <v>269.89999999999998</v>
+      </c>
+      <c r="C496" s="3">
+        <v>262.67</v>
+      </c>
+      <c r="H496" s="5">
+        <v>43660</v>
+      </c>
+    </row>
+    <row r="497" spans="1:9">
+      <c r="A497" s="2">
+        <f t="shared" si="237"/>
+        <v>772</v>
+      </c>
+      <c r="B497" s="3">
+        <v>270.25</v>
+      </c>
+      <c r="C497" s="3">
+        <v>244.1</v>
+      </c>
+      <c r="H497" s="5">
+        <v>43674</v>
+      </c>
+    </row>
+    <row r="498" spans="1:9">
+      <c r="A498" s="2">
+        <f t="shared" si="237"/>
+        <v>773</v>
+      </c>
+      <c r="B498" s="3">
+        <v>281.56</v>
+      </c>
+      <c r="C498" s="3">
+        <v>281.06</v>
+      </c>
+      <c r="D498" s="3">
+        <v>255.77</v>
+      </c>
+      <c r="E498" s="3">
+        <v>239.38</v>
+      </c>
+      <c r="H498" s="5">
+        <v>43688</v>
+      </c>
+      <c r="I498" s="5">
+        <v>43695</v>
+      </c>
+    </row>
+    <row r="499" spans="1:9">
+      <c r="A499" s="2">
+        <f t="shared" si="237"/>
+        <v>774</v>
+      </c>
+      <c r="B499" s="3">
+        <v>253.9</v>
+      </c>
+      <c r="C499" s="3">
+        <v>273.25</v>
+      </c>
+      <c r="D499" s="3">
+        <v>273.64</v>
+      </c>
+      <c r="E499" s="3">
+        <v>240.33</v>
+      </c>
+      <c r="H499" s="5">
+        <v>43702</v>
+      </c>
+      <c r="I499" s="5">
+        <v>43709</v>
+      </c>
+    </row>
+    <row r="500" spans="1:9">
+      <c r="A500" s="2">
+        <f t="shared" si="237"/>
+        <v>775</v>
+      </c>
+      <c r="B500" s="3">
+        <v>298.75</v>
+      </c>
+      <c r="C500" s="3">
+        <v>290.42</v>
+      </c>
+      <c r="H500" s="5">
+        <v>43716</v>
+      </c>
+    </row>
+    <row r="501" spans="1:9">
+      <c r="A501" s="2">
+        <f t="shared" si="237"/>
+        <v>776</v>
+      </c>
+      <c r="B501" s="3">
+        <v>257.77999999999997</v>
+      </c>
+      <c r="C501" s="3">
+        <v>282.87</v>
+      </c>
+      <c r="H501" s="5">
+        <v>43730</v>
+      </c>
+    </row>
+    <row r="502" spans="1:9">
+      <c r="A502" s="2">
+        <f t="shared" si="237"/>
+        <v>777</v>
+      </c>
+      <c r="D502" s="3">
+        <v>285.70999999999998</v>
+      </c>
+      <c r="E502" s="3">
+        <v>279.39</v>
+      </c>
+      <c r="I502" s="5">
+        <v>43737</v>
+      </c>
+    </row>
+    <row r="503" spans="1:9">
+      <c r="A503" s="2">
+        <f t="shared" si="237"/>
+        <v>778</v>
+      </c>
+      <c r="D503" s="3">
+        <v>188.8</v>
+      </c>
+      <c r="E503" s="3">
+        <v>213.2</v>
+      </c>
+      <c r="I503" s="5">
+        <v>43765</v>
+      </c>
+    </row>
+    <row r="504" spans="1:9">
+      <c r="A504" s="2">
+        <f t="shared" si="237"/>
+        <v>779</v>
+      </c>
+      <c r="B504" s="3">
+        <v>219.79</v>
+      </c>
+      <c r="C504" s="3">
+        <v>211.11</v>
+      </c>
+      <c r="H504" s="5">
+        <v>43758</v>
+      </c>
+    </row>
+    <row r="505" spans="1:9">
+      <c r="A505" s="2">
+        <f t="shared" si="237"/>
+        <v>780</v>
+      </c>
+      <c r="B505" s="3">
+        <v>220.74</v>
+      </c>
+      <c r="C505" s="3">
+        <v>198.67</v>
+      </c>
+      <c r="H505" s="5">
+        <v>43772</v>
       </c>
     </row>
   </sheetData>

--- a/data/wind tunnel/CURRENT WIND TUNNEL GENERATION MEANS.xlsx
+++ b/data/wind tunnel/CURRENT WIND TUNNEL GENERATION MEANS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/wind-tunnel-flies/data/wind tunnel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED4BB4B5-20B6-9C48-BB2A-A5EA61441344}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2184FE51-2F15-7549-8F3B-880CD12BDA5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="25920" windowHeight="13440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5740" yWindow="1440" windowWidth="25920" windowHeight="13440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Chart2" sheetId="1" r:id="rId1"/>
@@ -17264,244 +17264,384 @@
         <f>A443+1</f>
         <v>719</v>
       </c>
+      <c r="B444" s="3">
+        <v>289.69</v>
+      </c>
+      <c r="C444" s="3">
+        <v>300.63</v>
+      </c>
+      <c r="F444" s="4">
+        <f t="shared" ref="F444:F451" si="237">AVERAGE(B444:C444)</f>
+        <v>295.15999999999997</v>
+      </c>
     </row>
     <row r="445" spans="1:9">
       <c r="A445" s="2">
-        <f t="shared" ref="A445:A508" si="237">A444+1</f>
+        <f t="shared" ref="A445:A505" si="238">A444+1</f>
         <v>720</v>
+      </c>
+      <c r="B445" s="3">
+        <v>268.7</v>
+      </c>
+      <c r="C445" s="3">
+        <v>271.11</v>
+      </c>
+      <c r="D445" s="3">
+        <v>259.8</v>
+      </c>
+      <c r="E445" s="3">
+        <v>270.99</v>
+      </c>
+      <c r="F445" s="4">
+        <f t="shared" si="237"/>
+        <v>269.90499999999997</v>
+      </c>
+      <c r="G445" s="4">
+        <f t="shared" ref="G445" si="239">AVERAGE(D445:E445)</f>
+        <v>265.39499999999998</v>
       </c>
     </row>
     <row r="446" spans="1:9">
       <c r="A446" s="2">
+        <f t="shared" si="238"/>
+        <v>721</v>
+      </c>
+      <c r="B446" s="3">
+        <v>270.69</v>
+      </c>
+      <c r="C446" s="3">
+        <v>262.64</v>
+      </c>
+      <c r="D446" s="3">
+        <v>278.23</v>
+      </c>
+      <c r="E446" s="3">
+        <v>273.3</v>
+      </c>
+      <c r="F446" s="4">
         <f t="shared" si="237"/>
-        <v>721</v>
+        <v>266.66499999999996</v>
+      </c>
+      <c r="G446" s="4">
+        <f>AVERAGE(D446:E446)</f>
+        <v>275.76499999999999</v>
       </c>
     </row>
     <row r="447" spans="1:9">
       <c r="A447" s="2">
+        <f t="shared" si="238"/>
+        <v>722</v>
+      </c>
+      <c r="B447" s="3">
+        <v>291.79000000000002</v>
+      </c>
+      <c r="C447" s="3">
+        <v>286.3</v>
+      </c>
+      <c r="D447" s="3">
+        <v>237.59</v>
+      </c>
+      <c r="E447" s="3">
+        <v>251.17</v>
+      </c>
+      <c r="F447" s="4">
         <f t="shared" si="237"/>
-        <v>722</v>
+        <v>289.04500000000002</v>
+      </c>
+      <c r="G447" s="4">
+        <f>AVERAGE(D447:E447)</f>
+        <v>244.38</v>
       </c>
     </row>
     <row r="448" spans="1:9">
       <c r="A448" s="2">
+        <f t="shared" si="238"/>
+        <v>723</v>
+      </c>
+      <c r="B448" s="3">
+        <v>282.86</v>
+      </c>
+      <c r="C448" s="3">
+        <v>289.33999999999997</v>
+      </c>
+      <c r="D448" s="3">
+        <v>296.70999999999998</v>
+      </c>
+      <c r="E448" s="3">
+        <v>293.95999999999998</v>
+      </c>
+      <c r="F448" s="4">
         <f t="shared" si="237"/>
-        <v>723</v>
-      </c>
-    </row>
-    <row r="449" spans="1:1">
+        <v>286.10000000000002</v>
+      </c>
+      <c r="G448" s="4">
+        <f>AVERAGE(D448:E448)</f>
+        <v>295.33499999999998</v>
+      </c>
+    </row>
+    <row r="449" spans="1:7">
       <c r="A449" s="2">
+        <f t="shared" si="238"/>
+        <v>724</v>
+      </c>
+      <c r="B449" s="3">
+        <v>282.58999999999997</v>
+      </c>
+      <c r="C449" s="3">
+        <v>286.13</v>
+      </c>
+      <c r="D449" s="3">
+        <v>272.88</v>
+      </c>
+      <c r="E449" s="3">
+        <v>274.41000000000003</v>
+      </c>
+      <c r="F449" s="4">
         <f t="shared" si="237"/>
-        <v>724</v>
-      </c>
-    </row>
-    <row r="450" spans="1:1">
+        <v>284.36</v>
+      </c>
+      <c r="G449" s="4">
+        <f>AVERAGE(D449:E449)</f>
+        <v>273.64499999999998</v>
+      </c>
+    </row>
+    <row r="450" spans="1:7">
       <c r="A450" s="2">
+        <f t="shared" si="238"/>
+        <v>725</v>
+      </c>
+      <c r="B450" s="3">
+        <v>258.94</v>
+      </c>
+      <c r="C450" s="3">
+        <v>266.35000000000002</v>
+      </c>
+      <c r="D450" s="3">
+        <v>257.95999999999998</v>
+      </c>
+      <c r="E450" s="3">
+        <v>273.25</v>
+      </c>
+      <c r="F450" s="4">
         <f t="shared" si="237"/>
-        <v>725</v>
-      </c>
-    </row>
-    <row r="451" spans="1:1">
+        <v>262.64499999999998</v>
+      </c>
+      <c r="G450" s="4">
+        <f>AVERAGE(D450:E450)</f>
+        <v>265.60500000000002</v>
+      </c>
+    </row>
+    <row r="451" spans="1:7">
       <c r="A451" s="2">
+        <f t="shared" si="238"/>
+        <v>726</v>
+      </c>
+      <c r="B451" s="3">
+        <v>297.24</v>
+      </c>
+      <c r="C451" s="3">
+        <v>313.69</v>
+      </c>
+      <c r="F451" s="4">
         <f t="shared" si="237"/>
-        <v>726</v>
-      </c>
-    </row>
-    <row r="452" spans="1:1">
+        <v>305.46500000000003</v>
+      </c>
+    </row>
+    <row r="452" spans="1:7">
       <c r="A452" s="2">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>727</v>
       </c>
     </row>
-    <row r="453" spans="1:1">
+    <row r="453" spans="1:7">
       <c r="A453" s="2">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>728</v>
       </c>
     </row>
-    <row r="454" spans="1:1">
+    <row r="454" spans="1:7">
       <c r="A454" s="2">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>729</v>
       </c>
     </row>
-    <row r="455" spans="1:1">
+    <row r="455" spans="1:7">
       <c r="A455" s="2">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>730</v>
       </c>
     </row>
-    <row r="456" spans="1:1">
+    <row r="456" spans="1:7">
       <c r="A456" s="2">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>731</v>
       </c>
     </row>
-    <row r="457" spans="1:1">
+    <row r="457" spans="1:7">
       <c r="A457" s="2">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>732</v>
       </c>
     </row>
-    <row r="458" spans="1:1">
+    <row r="458" spans="1:7">
       <c r="A458" s="2">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>733</v>
       </c>
     </row>
-    <row r="459" spans="1:1">
+    <row r="459" spans="1:7">
       <c r="A459" s="2">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>734</v>
       </c>
     </row>
-    <row r="460" spans="1:1">
+    <row r="460" spans="1:7">
       <c r="A460" s="2">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>735</v>
       </c>
     </row>
-    <row r="461" spans="1:1">
+    <row r="461" spans="1:7">
       <c r="A461" s="2">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>736</v>
       </c>
     </row>
-    <row r="462" spans="1:1">
+    <row r="462" spans="1:7">
       <c r="A462" s="2">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>737</v>
       </c>
     </row>
-    <row r="463" spans="1:1">
+    <row r="463" spans="1:7">
       <c r="A463" s="2">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>738</v>
       </c>
     </row>
-    <row r="464" spans="1:1">
+    <row r="464" spans="1:7">
       <c r="A464" s="2">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>739</v>
       </c>
     </row>
     <row r="465" spans="1:1">
       <c r="A465" s="2">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>740</v>
       </c>
     </row>
     <row r="466" spans="1:1">
       <c r="A466" s="2">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>741</v>
       </c>
     </row>
     <row r="467" spans="1:1">
       <c r="A467" s="2">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>742</v>
       </c>
     </row>
     <row r="468" spans="1:1">
       <c r="A468" s="2">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>743</v>
       </c>
     </row>
     <row r="469" spans="1:1">
       <c r="A469" s="2">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>744</v>
       </c>
     </row>
     <row r="470" spans="1:1">
       <c r="A470" s="2">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>745</v>
       </c>
     </row>
     <row r="471" spans="1:1">
       <c r="A471" s="2">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>746</v>
       </c>
     </row>
     <row r="472" spans="1:1">
       <c r="A472" s="2">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>747</v>
       </c>
     </row>
     <row r="473" spans="1:1">
       <c r="A473" s="2">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>748</v>
       </c>
     </row>
     <row r="474" spans="1:1">
       <c r="A474" s="2">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>749</v>
       </c>
     </row>
     <row r="475" spans="1:1">
       <c r="A475" s="2">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>750</v>
       </c>
     </row>
     <row r="476" spans="1:1">
       <c r="A476" s="2">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>751</v>
       </c>
     </row>
     <row r="477" spans="1:1">
       <c r="A477" s="2">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>752</v>
       </c>
     </row>
     <row r="478" spans="1:1">
       <c r="A478" s="2">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>753</v>
       </c>
     </row>
     <row r="479" spans="1:1">
       <c r="A479" s="2">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>754</v>
       </c>
     </row>
     <row r="480" spans="1:1">
       <c r="A480" s="2">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>755</v>
       </c>
     </row>
     <row r="481" spans="1:9">
       <c r="A481" s="2">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>756</v>
       </c>
     </row>
     <row r="482" spans="1:9">
       <c r="A482" s="2">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>757</v>
       </c>
     </row>
     <row r="483" spans="1:9">
       <c r="A483" s="2">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>758</v>
       </c>
     </row>
     <row r="484" spans="1:9">
       <c r="A484" s="2">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>759</v>
       </c>
       <c r="D484" s="3">
@@ -17516,13 +17656,13 @@
     </row>
     <row r="485" spans="1:9">
       <c r="A485" s="2">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>760</v>
       </c>
     </row>
     <row r="486" spans="1:9">
       <c r="A486" s="2">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>761</v>
       </c>
       <c r="D486" s="3">
@@ -17537,13 +17677,13 @@
     </row>
     <row r="487" spans="1:9">
       <c r="A487" s="2">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>762</v>
       </c>
     </row>
     <row r="488" spans="1:9">
       <c r="A488" s="2">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>763</v>
       </c>
       <c r="D488" s="3">
@@ -17558,13 +17698,13 @@
     </row>
     <row r="489" spans="1:9">
       <c r="A489" s="2">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>764</v>
       </c>
     </row>
     <row r="490" spans="1:9">
       <c r="A490" s="2">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>765</v>
       </c>
       <c r="D490" s="3">
@@ -17579,19 +17719,19 @@
     </row>
     <row r="491" spans="1:9">
       <c r="A491" s="2">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>766</v>
       </c>
     </row>
     <row r="492" spans="1:9">
       <c r="A492" s="2">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>767</v>
       </c>
     </row>
     <row r="493" spans="1:9">
       <c r="A493" s="2">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>768</v>
       </c>
       <c r="D493" s="3">
@@ -17606,7 +17746,7 @@
     </row>
     <row r="494" spans="1:9">
       <c r="A494" s="2">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>769</v>
       </c>
       <c r="B494" s="3">
@@ -17630,7 +17770,7 @@
     </row>
     <row r="495" spans="1:9">
       <c r="A495" s="2">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>770</v>
       </c>
       <c r="B495" s="3">
@@ -17645,7 +17785,7 @@
     </row>
     <row r="496" spans="1:9">
       <c r="A496" s="2">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>771</v>
       </c>
       <c r="B496" s="3">
@@ -17660,7 +17800,7 @@
     </row>
     <row r="497" spans="1:9">
       <c r="A497" s="2">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>772</v>
       </c>
       <c r="B497" s="3">
@@ -17675,7 +17815,7 @@
     </row>
     <row r="498" spans="1:9">
       <c r="A498" s="2">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>773</v>
       </c>
       <c r="B498" s="3">
@@ -17699,7 +17839,7 @@
     </row>
     <row r="499" spans="1:9">
       <c r="A499" s="2">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>774</v>
       </c>
       <c r="B499" s="3">
@@ -17723,7 +17863,7 @@
     </row>
     <row r="500" spans="1:9">
       <c r="A500" s="2">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>775</v>
       </c>
       <c r="B500" s="3">
@@ -17738,7 +17878,7 @@
     </row>
     <row r="501" spans="1:9">
       <c r="A501" s="2">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>776</v>
       </c>
       <c r="B501" s="3">
@@ -17753,7 +17893,7 @@
     </row>
     <row r="502" spans="1:9">
       <c r="A502" s="2">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>777</v>
       </c>
       <c r="D502" s="3">
@@ -17768,7 +17908,7 @@
     </row>
     <row r="503" spans="1:9">
       <c r="A503" s="2">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>778</v>
       </c>
       <c r="D503" s="3">
@@ -17783,7 +17923,7 @@
     </row>
     <row r="504" spans="1:9">
       <c r="A504" s="2">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>779</v>
       </c>
       <c r="B504" s="3">
@@ -17798,7 +17938,7 @@
     </row>
     <row r="505" spans="1:9">
       <c r="A505" s="2">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>780</v>
       </c>
       <c r="B505" s="3">
